--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1909-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1909-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6233C438-372D-4E85-A47A-6C1281D0BB0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{290ACC82-7D3C-4D7F-84BE-890436F869A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{8F3FA7C7-0D1D-4BE2-91CF-7DF521A48B0D}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{6D2BD2BE-648C-42A4-AF13-46EF43E709A1}"/>
   </bookViews>
   <sheets>
     <sheet name="1909-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1511,30 +1511,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07E3B9FD-9CA4-4083-A566-CA8D45A897E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CECC3B2-69BA-4603-A5F7-E17D421DFEBC}">
   <dimension ref="A1:X65"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1568,7 +1568,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1604,7 +1604,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1724,7 +1724,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1944,7 +1944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2024</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2238,7 +2238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2023</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2022</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>1.83</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>1.83</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>29</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>29</v>
       </c>
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2021</v>
       </c>
@@ -2898,7 +2898,7 @@
         <v>8.39</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -2972,7 +2972,7 @@
         <v>8.39</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>29</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
@@ -3120,7 +3120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2020</v>
       </c>
@@ -3192,7 +3192,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>29</v>
       </c>
@@ -3266,7 +3266,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>29</v>
       </c>
@@ -3340,7 +3340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>29</v>
       </c>
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2019</v>
       </c>
@@ -3486,7 +3486,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>29</v>
       </c>
@@ -3560,7 +3560,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>29</v>
       </c>
@@ -3634,7 +3634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2018</v>
       </c>
@@ -3706,7 +3706,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>2017</v>
       </c>
@@ -3778,7 +3778,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2016</v>
       </c>
@@ -3850,7 +3850,7 @@
         <v>9.11</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="35">
         <v>2015</v>
       </c>
@@ -3922,7 +3922,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>2014</v>
       </c>
@@ -3994,7 +3994,7 @@
         <v>9.16</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="35">
         <v>2013</v>
       </c>
@@ -4066,7 +4066,7 @@
         <v>6.23</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>2012</v>
       </c>
@@ -4138,7 +4138,7 @@
         <v>5.01</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="35">
         <v>2011</v>
       </c>
@@ -4210,7 +4210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>2010</v>
       </c>
@@ -4282,7 +4282,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="35">
         <v>2009</v>
       </c>
@@ -4354,7 +4354,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>2008</v>
       </c>
@@ -4426,7 +4426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="35">
         <v>2007</v>
       </c>
@@ -4498,7 +4498,7 @@
         <v>9.26</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="37">
         <v>2006</v>
       </c>
@@ -4570,7 +4570,7 @@
         <v>8.23</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="35">
         <v>2005</v>
       </c>
@@ -4642,7 +4642,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="37">
         <v>2004</v>
       </c>
@@ -4714,7 +4714,7 @@
         <v>9.06</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="35">
         <v>2003</v>
       </c>
@@ -4786,7 +4786,7 @@
         <v>3.45</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="37">
         <v>2002</v>
       </c>
@@ -4858,7 +4858,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="35">
         <v>2001</v>
       </c>
@@ -4930,7 +4930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="37">
         <v>2000</v>
       </c>
@@ -5002,7 +5002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="35">
         <v>1999</v>
       </c>
@@ -5074,7 +5074,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="37">
         <v>1998</v>
       </c>
@@ -5146,7 +5146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="35">
         <v>1997</v>
       </c>
@@ -5218,7 +5218,7 @@
         <v>9.8800000000000008</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="37">
         <v>1996</v>
       </c>
@@ -5290,7 +5290,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="35">
         <v>1995</v>
       </c>
@@ -5362,7 +5362,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="37">
         <v>1994</v>
       </c>
@@ -5434,7 +5434,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="35">
         <v>1993</v>
       </c>
@@ -5506,7 +5506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="37">
         <v>1992</v>
       </c>
@@ -5578,7 +5578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="35">
         <v>1991</v>
       </c>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="37">
         <v>1990</v>
       </c>
@@ -5722,7 +5722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="35">
         <v>1989</v>
       </c>
@@ -5794,7 +5794,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="37">
         <v>1987</v>
       </c>
@@ -5866,7 +5866,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A62" s="35">
         <v>1986</v>
       </c>
@@ -5938,7 +5938,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A63" s="37">
         <v>1984</v>
       </c>
@@ -6010,7 +6010,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A64" s="35">
         <v>1983</v>
       </c>
@@ -6082,7 +6082,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A65" s="37" t="s">
         <v>58</v>
       </c>
